--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487559_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487559_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1853</v>
+        <v>3.2271</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3823</v>
+        <v>3.2371</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1971</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1.7756</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7058</v>
+        <v>0.7477</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7463</v>
+        <v>0.6011</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0405</v>
+        <v>0.1466</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4905</v>
+        <v>1.7533</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9977</v>
+        <v>1.3407</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4928</v>
+        <v>0.4126</v>
       </c>
       <c r="G3" t="n">
         <v>1.0366</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.1292</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1445</v>
+        <v>0.4876</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2781</v>
+        <v>-0.3583</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5665</v>
+        <v>-0.1623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5471</v>
+        <v>1.6607</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1136</v>
+        <v>-1.823</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3448</v>
+        <v>0.4261</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1783</v>
+        <v>-0.3718</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1665</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4541</v>
+        <v>2.2271</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9747</v>
+        <v>0.5104</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5206</v>
+        <v>1.7167</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7989</v>
+        <v>-1.801</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.153</v>
+        <v>-0.8822</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6459</v>
+        <v>-0.9188</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1539</v>
+        <v>-0.1172</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0722</v>
+        <v>0.4129</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9182</v>
+        <v>-0.5301</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2856</v>
+        <v>-1.0468</v>
       </c>
       <c r="E5" t="n">
-        <v>0.885</v>
+        <v>-1.6754</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1705</v>
+        <v>0.6286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4261</v>
+        <v>-2.118</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3718</v>
+        <v>-1.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7979000000000001</v>
+        <v>-1.0812</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2271</v>
+        <v>-1.9242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5104</v>
+        <v>-1.242</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7167</v>
+        <v>-0.6822</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.801</v>
+        <v>-0.1938</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8822</v>
+        <v>0.2052</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9188</v>
+        <v>-0.399</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2404</v>
+        <v>0.2877</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3629</v>
+        <v>0.2488</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8776</v>
+        <v>0.039</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4295</v>
+        <v>-1.0884</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0848</v>
+        <v>0.0519</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6553</v>
+        <v>-1.1403</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.118</v>
+        <v>-1.3448</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0368</v>
+        <v>-0.1783</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0812</v>
+        <v>-1.1665</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9242</v>
+        <v>0.4541</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.242</v>
+        <v>0.9747</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6822</v>
+        <v>-0.5206</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1938</v>
+        <v>-1.7989</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2052</v>
+        <v>-1.153</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.399</v>
+        <v>-0.6459</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0949</v>
+        <v>-0.368</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1606</v>
+        <v>0.577</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06569999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8235</v>
+        <v>-1.9558</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1922</v>
+        <v>-0.0304</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6313</v>
+        <v>-1.9254</v>
       </c>
       <c r="G7" t="n">
         <v>-3.9298</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5521</v>
+        <v>0.4198</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1347</v>
+        <v>0.2964</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4174</v>
+        <v>0.1234</v>
       </c>
       <c r="V7" t="n">
         <v>3.3169</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.5689</v>
+        <v>-6.1464</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.5403</v>
+        <v>-6.5832</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9714</v>
+        <v>0.4368</v>
       </c>
       <c r="G8" t="n">
         <v>-4.0275</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9263</v>
+        <v>0.3488</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5087</v>
+        <v>0.4658</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4176</v>
+        <v>-0.117</v>
       </c>
       <c r="V8" t="n">
         <v>0.6659</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.544</v>
+        <v>-6.244</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4976</v>
+        <v>-4.4382</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0464</v>
+        <v>-1.8058</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0924</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8847</v>
+        <v>-0.5848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.31</v>
+        <v>-0.2506</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5748</v>
+        <v>-0.3342</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4332</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.597</v>
+        <v>-6.8817</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8807</v>
+        <v>-4.3526</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7163</v>
+        <v>-2.5291</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6051</v>
@@ -1234,13 +1234,13 @@
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8963</v>
+        <v>-0.181</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1735</v>
+        <v>0.3546</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7228</v>
+        <v>-0.5356</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9412</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.1392</v>
+        <v>-18.545</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.3835</v>
+        <v>-10.7894</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.755700000000001</v>
+        <v>-7.7555</v>
       </c>
       <c r="G11" t="n">
         <v>-11.8793</v>
@@ -1288,7 +1288,7 @@
         <v>-1.5826</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.4942</v>
+        <v>-5.494199999999999</v>
       </c>
       <c r="L11" t="n">
         <v>3.9117</v>
@@ -1312,13 +1312,13 @@
         <v>12.73</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08820000000000006</v>
+        <v>0.6822000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5994</v>
+        <v>3.1936</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5113</v>
+        <v>-2.5112</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4930999999999996</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3927</v>
+        <v>6.1592</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4793</v>
+        <v>2.9561</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9134</v>
+        <v>3.2031</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6744</v>
+        <v>3.82</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0185</v>
+        <v>5.7558</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6559</v>
+        <v>-1.9358</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4328</v>
+        <v>2.8243</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2127</v>
+        <v>3.8414</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6455</v>
+        <v>-1.0171</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2415</v>
+        <v>0.9956</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2311</v>
+        <v>1.9144</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0104</v>
+        <v>-0.9188</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9377</v>
+        <v>0.5875</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1958</v>
+        <v>-2.1543</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1336</v>
+        <v>2.7419</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2194</v>
+        <v>-0.4061</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2423</v>
+        <v>-0.147</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4617</v>
+        <v>-0.2591</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9165</v>
+        <v>6.1551</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9328</v>
+        <v>1.8886</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9837</v>
+        <v>4.2665</v>
       </c>
       <c r="G13" t="n">
-        <v>3.82</v>
+        <v>2.6744</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7558</v>
+        <v>1.0185</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9358</v>
+        <v>1.6559</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8243</v>
+        <v>1.4328</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8414</v>
+        <v>-0.2127</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0171</v>
+        <v>1.6455</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9956</v>
+        <v>1.2415</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9144</v>
+        <v>1.2311</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9188</v>
+        <v>0.0104</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5875</v>
+        <v>2.9377</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1543</v>
+        <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7419</v>
+        <v>3.1336</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6489</v>
+        <v>0.543</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1704</v>
+        <v>0.6516</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4785</v>
+        <v>-0.1087</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1578</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1086</v>
+        <v>3.4131</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6709</v>
+        <v>2.6451</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4378</v>
+        <v>0.768</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0231</v>
+        <v>3.6798</v>
       </c>
       <c r="H14" t="n">
-        <v>1.573</v>
+        <v>0.3406</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4501</v>
+        <v>3.3392</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2586</v>
+        <v>3.5361</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8845</v>
+        <v>0.3385</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3741</v>
+        <v>3.1976</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2355</v>
+        <v>0.1437</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6885</v>
+        <v>0.0021</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.924</v>
+        <v>0.1416</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1016</v>
+        <v>0.246</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7785</v>
+        <v>0.0882</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3231</v>
+        <v>0.1578</v>
       </c>
       <c r="V14" t="n">
-        <v>1.159</v>
+        <v>-1.492</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.001</v>
+        <v>3.1212</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2358</v>
+        <v>3.279</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7652</v>
+        <v>-0.1578</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6798</v>
+        <v>3.0058</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3406</v>
+        <v>2.556</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3392</v>
+        <v>0.4498</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5361</v>
+        <v>3.4527</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3385</v>
+        <v>2.0738</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1976</v>
+        <v>1.3789</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1437</v>
+        <v>-0.4469</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0021</v>
+        <v>0.4822</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1416</v>
+        <v>-0.9292</v>
       </c>
       <c r="P15" t="n">
         <v>0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1661</v>
+        <v>0.3527</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3211</v>
+        <v>0.5681</v>
       </c>
       <c r="U15" t="n">
-        <v>0.155</v>
+        <v>-0.2154</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.492</v>
+        <v>-1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7737</v>
+        <v>2.748</v>
       </c>
       <c r="E16" t="n">
-        <v>3.279</v>
+        <v>1.5452</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5053</v>
+        <v>1.2028</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0058</v>
+        <v>2.0231</v>
       </c>
       <c r="H16" t="n">
-        <v>2.556</v>
+        <v>1.573</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4498</v>
+        <v>0.4501</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4527</v>
+        <v>2.2586</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0738</v>
+        <v>0.8845</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3789</v>
+        <v>1.3741</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4469</v>
+        <v>-0.2355</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4822</v>
+        <v>0.6885</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9292</v>
+        <v>-0.924</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9377</v>
+        <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0052</v>
+        <v>0.7409</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5681</v>
+        <v>0.6528</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5629</v>
+        <v>0.0881</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2166</v>
+        <v>1.159</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2166</v>
+        <v>1.7673</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4332</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3786</v>
+        <v>1.5343</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5074</v>
+        <v>0.6097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8712</v>
+        <v>0.9246</v>
       </c>
       <c r="G17" t="n">
         <v>0.2096</v>
@@ -1780,13 +1780,13 @@
         <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0061</v>
+        <v>0.1497</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0418</v>
+        <v>0.0606</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1222</v>
+        <v>0.9573</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9526</v>
+        <v>-3.2596</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0748</v>
+        <v>4.2168</v>
       </c>
       <c r="G18" t="n">
         <v>-2.567</v>
@@ -1858,13 +1858,13 @@
         <v>3.7211</v>
       </c>
       <c r="S18" t="n">
-        <v>1.021</v>
+        <v>0.856</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7752</v>
+        <v>0.4681</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2459</v>
+        <v>0.3879</v>
       </c>
       <c r="V18" t="n">
         <v>1.1014</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1628</v>
+        <v>-0.3067</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7037</v>
+        <v>0.3967</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8665</v>
+        <v>-0.7033</v>
       </c>
       <c r="G19" t="n">
         <v>-0.667</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5042</v>
+        <v>0.3604</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6228</v>
+        <v>0.3158</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1186</v>
+        <v>0.0446</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1737</v>
+        <v>-1.2875</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1458</v>
+        <v>-1.9395</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3195</v>
+        <v>0.652</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4665</v>
+        <v>0.1673</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5138</v>
+        <v>0.6574</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9803</v>
+        <v>-0.4902</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2914</v>
+        <v>-0.5962</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0326</v>
+        <v>0.0408</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3241</v>
+        <v>-0.637</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1751</v>
+        <v>0.7634</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4812</v>
+        <v>0.6166</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6563</v>
+        <v>0.1468</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R20" t="n">
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3742</v>
+        <v>-0.3752</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5328000000000001</v>
+        <v>-0.1682</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9071</v>
+        <v>-0.207</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3329</v>
+        <v>-0.8837</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2177</v>
+        <v>-1.3083</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2465</v>
+        <v>-0.3658</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0288</v>
+        <v>-0.9425</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1673</v>
+        <v>-0.4665</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6574</v>
+        <v>1.5138</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4902</v>
+        <v>-1.9803</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5962</v>
+        <v>-0.2914</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0408</v>
+        <v>1.0326</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.637</v>
+        <v>-1.3241</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7634</v>
+        <v>-0.1751</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6166</v>
+        <v>0.4812</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1468</v>
+        <v>-0.6563</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3054</v>
+        <v>-0.5089</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4752</v>
+        <v>0.0212</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8302</v>
+        <v>-0.5301</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8837</v>
+        <v>-0.3329</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>19.1391</v>
+        <v>21.1857</v>
       </c>
       <c r="E22" t="n">
-        <v>7.755599999999998</v>
+        <v>7.755499999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>11.3836</v>
+        <v>13.4302</v>
       </c>
       <c r="G22" t="n">
         <v>11.8795</v>
@@ -2146,16 +2146,16 @@
         <v>10.2966</v>
       </c>
       <c r="K22" t="n">
-        <v>7.8015</v>
+        <v>7.801500000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>2.4952</v>
+        <v>2.495200000000001</v>
       </c>
       <c r="M22" t="n">
         <v>1.5824</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4942</v>
+        <v>5.494200000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-3.9119</v>
@@ -2167,16 +2167,16 @@
         <v>-12.73</v>
       </c>
       <c r="R22" t="n">
-        <v>19.5848</v>
+        <v>19.58479999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.08810000000000007</v>
+        <v>1.9585</v>
       </c>
       <c r="T22" t="n">
         <v>2.5112</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.5994</v>
+        <v>-0.5528</v>
       </c>
       <c r="V22" t="n">
         <v>0.493</v>
@@ -2185,7 +2185,7 @@
         <v>7.6776</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.184599999999999</v>
+        <v>-7.1846</v>
       </c>
     </row>
   </sheetData>
